--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_46_R5.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_46_R5.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9555</v>
+        <v>4.5446</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3144</v>
+        <v>2.6682</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6411</v>
+        <v>1.8764</v>
       </c>
       <c r="G2" t="n">
         <v>2.6673</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0855</v>
+        <v>-0.4964</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2161</v>
+        <v>0.1377</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8694</v>
+        <v>-0.6341</v>
       </c>
       <c r="V2" t="n">
         <v>1.214</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. STRAZEL</t>
+          <t>D. THEIS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1493</v>
+        <v>2.0049</v>
       </c>
       <c r="E3" t="n">
-        <v>1.926</v>
+        <v>3.5013</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2233</v>
+        <v>-1.4964</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4594</v>
+        <v>3.2797</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1741</v>
+        <v>1.9713</v>
       </c>
       <c r="I3" t="n">
-        <v>2.2853</v>
+        <v>1.3084</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8347</v>
+        <v>4.1089</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1246</v>
+        <v>2.2687</v>
       </c>
       <c r="L3" t="n">
-        <v>2.7101</v>
+        <v>1.8402</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3754</v>
+        <v>-0.8293</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0495</v>
+        <v>-0.2974</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4248</v>
+        <v>-0.5319</v>
       </c>
       <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>-1.1598</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-2.5515</v>
-      </c>
       <c r="R3" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1718</v>
+        <v>-0.4551</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4288</v>
+        <v>0.016</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.257</v>
+        <v>-0.4711</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6778999999999999</v>
+        <v>-0.8197</v>
       </c>
       <c r="W3" t="n">
-        <v>1.214</v>
+        <v>0.5361</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5361</v>
+        <v>-1.3558</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. TARPEY</t>
+          <t>A. DIALLO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9821</v>
+        <v>1.9472</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6327</v>
+        <v>2.6327</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3494</v>
+        <v>-0.6855</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6352</v>
+        <v>2.2839</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3374</v>
+        <v>2.983</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2978</v>
+        <v>-0.6992</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0704</v>
+        <v>3.2952</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0336</v>
+        <v>2.8302</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0368</v>
+        <v>0.465</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5648</v>
+        <v>-1.0114</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3038</v>
+        <v>0.1528</v>
       </c>
       <c r="O4" t="n">
-        <v>0.261</v>
+        <v>-1.1642</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6959</v>
+        <v>2.5515</v>
       </c>
       <c r="S4" t="n">
-        <v>0.651</v>
+        <v>-1.1923</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5623</v>
+        <v>-0.0389</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0887</v>
+        <v>-1.1534</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. THEIS</t>
+          <t>M. STRAZEL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9131</v>
+        <v>1.947</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3087</v>
+        <v>1.6901</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.3956</v>
+        <v>0.2569</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2797</v>
+        <v>2.4594</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9713</v>
+        <v>0.1741</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3084</v>
+        <v>2.2853</v>
       </c>
       <c r="J5" t="n">
-        <v>4.1089</v>
+        <v>2.8347</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2687</v>
+        <v>0.1246</v>
       </c>
       <c r="L5" t="n">
-        <v>1.8402</v>
+        <v>2.7101</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8293</v>
+        <v>-0.3754</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2974</v>
+        <v>0.0495</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5319</v>
+        <v>-0.4248</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>-2.5515</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5469000000000001</v>
+        <v>-0.0305</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1766</v>
+        <v>0.1928</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3703</v>
+        <v>-0.2234</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.8197</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5361</v>
+        <v>1.214</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.3558</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. MIROTIC</t>
+          <t>K. HAYES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6874</v>
+        <v>1.5981</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0193</v>
+        <v>0.9494</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7066</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5601</v>
+        <v>1.503</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0118</v>
+        <v>1.4861</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4517</v>
+        <v>0.0168</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2836</v>
+        <v>0.9846</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1113</v>
+        <v>0.911</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.3949</v>
+        <v>0.0736</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8437</v>
+        <v>0.5184</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9005</v>
+        <v>0.5752</v>
       </c>
       <c r="O6" t="n">
         <v>-0.0568</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.8556</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.5515</v>
+        <v>-0.232</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5515</v>
+        <v>2.0876</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4494</v>
+        <v>-0.5465</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0657</v>
+        <v>0.1968</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6163</v>
+        <v>-0.7433</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6778999999999999</v>
+        <v>-1.214</v>
       </c>
       <c r="W6" t="n">
-        <v>1.7501</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. DIALLO</t>
+          <t>T. TARPEY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6867</v>
+        <v>1.561</v>
       </c>
       <c r="E7" t="n">
-        <v>2.2042</v>
+        <v>0.2789</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5174</v>
+        <v>1.2822</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2839</v>
+        <v>0.6352</v>
       </c>
       <c r="H7" t="n">
-        <v>2.983</v>
+        <v>0.3374</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6992</v>
+        <v>0.2978</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2952</v>
+        <v>0.0704</v>
       </c>
       <c r="K7" t="n">
-        <v>2.8302</v>
+        <v>0.0336</v>
       </c>
       <c r="L7" t="n">
-        <v>0.465</v>
+        <v>0.0368</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0114</v>
+        <v>0.5648</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1528</v>
+        <v>0.3038</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1642</v>
+        <v>0.261</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5515</v>
+        <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.4528</v>
+        <v>0.23</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4674</v>
+        <v>0.2084</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9853</v>
+        <v>0.0215</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. HAYES</t>
+          <t>N. MIROTIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4637</v>
+        <v>1.064</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9494</v>
+        <v>-0.609</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5143</v>
+        <v>1.673</v>
       </c>
       <c r="G8" t="n">
-        <v>1.503</v>
+        <v>0.5601</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4861</v>
+        <v>1.0118</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0168</v>
+        <v>-0.4517</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9846</v>
+        <v>-0.2836</v>
       </c>
       <c r="K8" t="n">
-        <v>0.911</v>
+        <v>0.1113</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0736</v>
+        <v>-0.3949</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5184</v>
+        <v>0.8437</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5752</v>
+        <v>0.9005</v>
       </c>
       <c r="O8" t="n">
         <v>-0.0568</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8556</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.232</v>
+        <v>-2.5515</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0876</v>
+        <v>2.5515</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6808999999999999</v>
+        <v>-0.174</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1968</v>
+        <v>0.476</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8777</v>
+        <v>-0.6499</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.214</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.7501</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2361</v>
+        <v>-2.9136</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5112</v>
+        <v>-2.0878</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7249</v>
+        <v>-0.8257</v>
       </c>
       <c r="G9" t="n">
         <v>-2.3444</v>
@@ -1156,13 +1156,13 @@
         <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>1.8042</v>
+        <v>0.1267</v>
       </c>
       <c r="T9" t="n">
-        <v>2.1745</v>
+        <v>0.5979</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3703</v>
+        <v>-0.4711</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2627</v>
+        <v>-3.2108</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.9312</v>
+        <v>-3.9129</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6685</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="G10" t="n">
         <v>-2.795</v>
@@ -1234,13 +1234,13 @@
         <v>2.0876</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.3955</v>
+        <v>-1.3436</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2696</v>
+        <v>-0.2513</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1259</v>
+        <v>-1.0923</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.05</v>
+        <v>-4.8802</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.9658</v>
+        <v>-3.8296</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0842</v>
+        <v>-1.0506</v>
       </c>
       <c r="G11" t="n">
         <v>-4.9562</v>
@@ -1312,13 +1312,13 @@
         <v>1.8556</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.0063</v>
+        <v>-0.8364</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.411</v>
+        <v>-0.2748</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5952</v>
+        <v>-0.5616</v>
       </c>
       <c r="V11" t="n">
         <v>1.6083</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.289000000000002</v>
+        <v>3.6622</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9079000000000006</v>
+        <v>1.281299999999999</v>
       </c>
       <c r="F12" t="n">
         <v>2.3811</v>
@@ -1357,7 +1357,7 @@
         <v>3.293</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7904</v>
+        <v>2.790400000000001</v>
       </c>
       <c r="I12" t="n">
         <v>0.5023999999999997</v>
@@ -1390,10 +1390,10 @@
         <v>16.2368</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.0915</v>
+        <v>-4.7181</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8874000000000004</v>
+        <v>1.2606</v>
       </c>
       <c r="U12" t="n">
         <v>-5.9787</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,40 +1423,40 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.2827</v>
+        <v>4.0928</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8657</v>
+        <v>2.887</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4169</v>
+        <v>1.2058</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8914</v>
+        <v>2.932</v>
       </c>
       <c r="H13" t="n">
-        <v>3.5582</v>
+        <v>-0.0057</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.6668</v>
+        <v>2.9377</v>
       </c>
       <c r="J13" t="n">
-        <v>1.0883</v>
+        <v>2.1318</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2266</v>
+        <v>-0.6519</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.1382</v>
+        <v>2.7837</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1969</v>
+        <v>0.8002</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3317</v>
+        <v>0.6462</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5286</v>
+        <v>0.154</v>
       </c>
       <c r="P13" t="n">
         <v>1.3917</v>
@@ -1468,28 +1468,28 @@
         <v>1.3917</v>
       </c>
       <c r="S13" t="n">
-        <v>2.9995</v>
+        <v>0.8413</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7774</v>
+        <v>0.7551</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2221</v>
+        <v>0.0861</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.205</v>
+        <v>4.0112</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1793</v>
+        <v>0.8157</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0257</v>
+        <v>3.1954</v>
       </c>
       <c r="G14" t="n">
-        <v>2.932</v>
+        <v>0.3827</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0057</v>
+        <v>-0.8786</v>
       </c>
       <c r="I14" t="n">
-        <v>2.9377</v>
+        <v>1.2613</v>
       </c>
       <c r="J14" t="n">
-        <v>2.1318</v>
+        <v>-0.4926</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6519</v>
+        <v>-0.9173</v>
       </c>
       <c r="L14" t="n">
-        <v>2.7837</v>
+        <v>0.4247</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8002</v>
+        <v>0.8753</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6462</v>
+        <v>0.0387</v>
       </c>
       <c r="O14" t="n">
-        <v>0.154</v>
+        <v>0.8366</v>
       </c>
       <c r="P14" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0466</v>
+        <v>0.9326</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0474</v>
+        <v>0.2361</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.094</v>
+        <v>0.6965</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.0722</v>
+        <v>1.0722</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1291</v>
+        <v>3.9215</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.009900000000000001</v>
+        <v>4.5429</v>
       </c>
       <c r="F15" t="n">
-        <v>3.139</v>
+        <v>-0.6214</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3827</v>
+        <v>3.3965</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8786</v>
+        <v>2.9916</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2613</v>
+        <v>0.4049</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4926</v>
+        <v>3.2788</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.9173</v>
+        <v>2.1881</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4247</v>
+        <v>1.0907</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8753</v>
+        <v>0.1176</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0387</v>
+        <v>0.8035</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8366</v>
+        <v>-0.6859</v>
       </c>
       <c r="P15" t="n">
-        <v>1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0505</v>
+        <v>-0.1013</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5895</v>
+        <v>0.2794</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6401</v>
+        <v>-0.3806</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0722</v>
+        <v>0.3943</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0722</v>
+        <v>2.1444</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3609</v>
+        <v>3.8242</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5993</v>
+        <v>1.9221</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2384</v>
+        <v>1.9021</v>
       </c>
       <c r="G16" t="n">
-        <v>3.3965</v>
+        <v>0.8914</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9916</v>
+        <v>3.5582</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4049</v>
+        <v>-2.6668</v>
       </c>
       <c r="J16" t="n">
-        <v>3.2788</v>
+        <v>1.0883</v>
       </c>
       <c r="K16" t="n">
-        <v>2.1881</v>
+        <v>3.2266</v>
       </c>
       <c r="L16" t="n">
-        <v>1.0907</v>
+        <v>-2.1382</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1176</v>
+        <v>-0.1969</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8035</v>
+        <v>0.3317</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6859</v>
+        <v>-0.5286</v>
       </c>
       <c r="P16" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.6619</v>
+        <v>1.5411</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6642</v>
+        <v>0.8338</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9976</v>
+        <v>0.7073</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2311</v>
+        <v>-0.0499</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4846</v>
+        <v>1.0128</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2535</v>
+        <v>-1.0626</v>
       </c>
       <c r="G17" t="n">
         <v>3.1182</v>
@@ -1780,13 +1780,13 @@
         <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1129</v>
+        <v>-0.168</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1889</v>
+        <v>-0.2829</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.076</v>
+        <v>0.1149</v>
       </c>
       <c r="V17" t="n">
         <v>-1.6083</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. TAYLOR</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5618</v>
+        <v>-1.1626</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4926</v>
+        <v>0.3195</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0692</v>
+        <v>-1.4821</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9794</v>
+        <v>1.2998</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1595</v>
+        <v>2.6986</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8199</v>
+        <v>-1.3988</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6865</v>
+        <v>2.2938</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1379</v>
+        <v>3.4786</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5486</v>
+        <v>-1.1848</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6659</v>
+        <v>-0.9941</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2974</v>
+        <v>-0.78</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.3684</v>
+        <v>-0.214</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.3917</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3195</v>
+        <v>-3.4793</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9510999999999999</v>
+        <v>0.3932</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1404</v>
+        <v>0.4327</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1893</v>
+        <v>-0.0395</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1418</v>
+        <v>-0.5361</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1418</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9365</v>
+        <v>-1.797</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9934</v>
+        <v>-2.3473</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0569</v>
+        <v>0.5502</v>
       </c>
       <c r="G19" t="n">
         <v>-2.0537</v>
@@ -1936,13 +1936,13 @@
         <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0272</v>
+        <v>0.1122</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8496</v>
+        <v>0.4957</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8768</v>
+        <v>-0.3835</v>
       </c>
       <c r="V19" t="n">
         <v>1.0722</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>K. TAYLOR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9027</v>
+        <v>-1.8985</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.86</v>
+        <v>-0.7285</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0427</v>
+        <v>-1.17</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2998</v>
+        <v>-0.9794</v>
       </c>
       <c r="H20" t="n">
-        <v>2.6986</v>
+        <v>-0.1595</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3988</v>
+        <v>-0.8199</v>
       </c>
       <c r="J20" t="n">
-        <v>2.2938</v>
+        <v>0.6865</v>
       </c>
       <c r="K20" t="n">
-        <v>3.4786</v>
+        <v>0.1379</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.1848</v>
+        <v>0.5486</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9941</v>
+        <v>-1.6659</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.78</v>
+        <v>-0.2974</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.214</v>
+        <v>-1.3684</v>
       </c>
       <c r="P20" t="n">
+        <v>-1.3917</v>
+      </c>
+      <c r="Q20" t="n">
         <v>-2.3195</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-3.4793</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3469</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7468</v>
+        <v>0.9045</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6001</v>
+        <v>-0.2902</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5361</v>
+        <v>-0.1418</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.6083</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4451</v>
+        <v>-3.5152</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2954</v>
+        <v>-1.855</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1496</v>
+        <v>-1.6602</v>
       </c>
       <c r="G21" t="n">
-        <v>-6.3583</v>
+        <v>-2.9556</v>
       </c>
       <c r="H21" t="n">
-        <v>-6.3818</v>
+        <v>-2.9723</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0235</v>
+        <v>0.0167</v>
       </c>
       <c r="J21" t="n">
-        <v>-5.7538</v>
+        <v>-0.7033</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.9379</v>
+        <v>-1.7204</v>
       </c>
       <c r="L21" t="n">
-        <v>0.184</v>
+        <v>1.0171</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6044</v>
+        <v>-2.2522</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4439</v>
+        <v>-1.2518</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1605</v>
+        <v>-1.0004</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>2.6296</v>
+        <v>0.2084</v>
       </c>
       <c r="T21" t="n">
-        <v>3.1928</v>
+        <v>0.0081</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5632</v>
+        <v>0.2003</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2836</v>
+        <v>-0.5361</v>
       </c>
       <c r="W21" t="n">
-        <v>0.4254</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1418</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8153</v>
+        <v>-4.1019</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.8775</v>
+        <v>-3.2314</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9377</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>-2.9664</v>
@@ -2170,13 +2170,13 @@
         <v>0.4639</v>
       </c>
       <c r="S22" t="n">
-        <v>1.5428</v>
+        <v>1.2562</v>
       </c>
       <c r="T22" t="n">
-        <v>1.3645</v>
+        <v>1.0106</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1784</v>
+        <v>0.2456</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5361</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8361</v>
+        <v>-5.0406</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4447</v>
+        <v>-5.1826</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3913</v>
+        <v>0.142</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.9556</v>
+        <v>-6.3583</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.9723</v>
+        <v>-6.3818</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0167</v>
+        <v>0.0235</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7033</v>
+        <v>-5.7538</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.7204</v>
+        <v>-5.9379</v>
       </c>
       <c r="L23" t="n">
-        <v>1.0171</v>
+        <v>0.184</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.2522</v>
+        <v>-0.6044</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.2518</v>
+        <v>-0.4439</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0004</v>
+        <v>-0.1605</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1125</v>
+        <v>1.0341</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5816</v>
+        <v>1.3056</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4692</v>
+        <v>-0.2715</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.5361</v>
+        <v>0.2836</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.4254</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5361</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="24">
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2887</v>
+        <v>-1.716000000000003</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.8446</v>
+        <v>-1.844800000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.443900000000001</v>
+        <v>0.1286999999999995</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.292800000000001</v>
+        <v>-3.2928</v>
       </c>
       <c r="H24" t="n">
         <v>-2.7904</v>
@@ -2305,7 +2305,7 @@
         <v>-1.3889</v>
       </c>
       <c r="L24" t="n">
-        <v>2.943000000000001</v>
+        <v>2.943</v>
       </c>
       <c r="M24" t="n">
         <v>-4.8471</v>
@@ -2317,7 +2317,7 @@
         <v>-3.4455</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.4792</v>
+        <v>-3.479200000000001</v>
       </c>
       <c r="Q24" t="n">
         <v>-16.2367</v>
@@ -2326,13 +2326,13 @@
         <v>12.7574</v>
       </c>
       <c r="S24" t="n">
-        <v>5.091299999999999</v>
+        <v>6.664199999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>5.978900000000001</v>
+        <v>5.9787</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8872000000000002</v>
+        <v>0.6854</v>
       </c>
       <c r="V24" t="n">
         <v>-1.6083</v>
@@ -2341,7 +2341,7 @@
         <v>6.858600000000001</v>
       </c>
       <c r="X24" t="n">
-        <v>-8.466899999999999</v>
+        <v>-8.466900000000001</v>
       </c>
     </row>
   </sheetData>
